--- a/CARGO_DEPARTURE_MORNING.xlsx
+++ b/CARGO_DEPARTURE_MORNING.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fiona\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\fiona\optimisation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47F6AAA-BCCB-4176-8C2A-E00DE44D0B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91ABDD57-137F-4710-8C0E-5D4B26AD1080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4C96D902-8C59-4966-B0F7-AE5ADA9D8A6E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{4C96D902-8C59-4966-B0F7-AE5ADA9D8A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2094" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="33">
   <si>
     <t>Morning</t>
   </si>
@@ -148,7 +148,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-14809]hh:mm;@"/>
+    <numFmt numFmtId="164" formatCode="[$-14809]hh:mm;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -197,7 +197,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -457,19 +457,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -566,25 +605,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="84">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -659,391 +696,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1135,6 +787,405 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4600,47 +4651,47 @@
       <formula>#REF!&gt;=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:AW1">
+    <cfRule type="expression" dxfId="82" priority="62">
+      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="82" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="1" operator="equal">
       <formula>"DL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="2" operator="equal">
       <formula>"Dcar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="3" operator="equal">
       <formula>"DL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="4" operator="equal">
       <formula>"Dcar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="5" operator="equal">
       <formula>"DL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="6" operator="equal">
       <formula>"Dcar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="7" operator="equal">
       <formula>"DL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="8" operator="equal">
       <formula>"Dcar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="9" operator="equal">
       <formula>"DL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="10" operator="equal">
       <formula>"Dcar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="11" operator="equal">
       <formula>"DL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="12" operator="equal">
       <formula>"Dcar6"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AW1">
-    <cfRule type="expression" dxfId="0" priority="62">
-      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7610,51 +7661,51 @@
     <mergeCell ref="A2:AW2"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A4">
-    <cfRule type="expression" dxfId="70" priority="14">
+    <cfRule type="expression" dxfId="69" priority="14">
       <formula>#REF!&gt;=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:AW1">
+    <cfRule type="expression" dxfId="68" priority="60">
+      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="69" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="1" operator="equal">
       <formula>"DL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="2" operator="equal">
       <formula>"Dcar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="3" operator="equal">
       <formula>"DL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="4" operator="equal">
       <formula>"Dcar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="5" operator="equal">
       <formula>"DL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="6" operator="equal">
       <formula>"Dcar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="7" operator="equal">
       <formula>"DL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="8" operator="equal">
       <formula>"Dcar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="9" operator="equal">
       <formula>"DL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="10" operator="equal">
       <formula>"Dcar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="57" priority="11" operator="equal">
       <formula>"DL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="12" operator="equal">
       <formula>"Dcar6"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AW1">
-    <cfRule type="expression" dxfId="57" priority="60">
-      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10636,51 +10687,51 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A4">
-    <cfRule type="expression" dxfId="56" priority="14">
+    <cfRule type="expression" dxfId="55" priority="14">
       <formula>#REF!&gt;=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:AW1">
+    <cfRule type="expression" dxfId="54" priority="61">
+      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="1" operator="equal">
       <formula>"DL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="2" operator="equal">
       <formula>"Dcar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
       <formula>"DL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="4" operator="equal">
       <formula>"Dcar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="5" operator="equal">
       <formula>"DL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="6" operator="equal">
       <formula>"Dcar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="7" operator="equal">
       <formula>"DL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="8" operator="equal">
       <formula>"Dcar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="9" operator="equal">
       <formula>"DL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="10" operator="equal">
       <formula>"Dcar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="11" operator="equal">
       <formula>"DL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="12" operator="equal">
       <formula>"Dcar6"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AW1">
-    <cfRule type="expression" dxfId="43" priority="61">
-      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13674,51 +13725,51 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A4">
-    <cfRule type="expression" dxfId="42" priority="14">
+    <cfRule type="expression" dxfId="41" priority="14">
       <formula>#REF!&gt;=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:AW1">
+    <cfRule type="expression" dxfId="40" priority="59">
+      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
       <formula>"DL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
       <formula>"Dcar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="3" operator="equal">
       <formula>"DL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="4" operator="equal">
       <formula>"Dcar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="5" operator="equal">
       <formula>"DL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="6" operator="equal">
       <formula>"Dcar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="equal">
       <formula>"DL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="equal">
       <formula>"Dcar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="9" operator="equal">
       <formula>"DL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="10" operator="equal">
       <formula>"Dcar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="11" operator="equal">
       <formula>"DL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="12" operator="equal">
       <formula>"Dcar6"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AW1">
-    <cfRule type="expression" dxfId="29" priority="59">
-      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13952,10 +14003,10 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="38" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="26" t="s">
@@ -14101,10 +14152,10 @@
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="39" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="24" t="s">
@@ -14250,10 +14301,10 @@
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="28" t="s">
+      <c r="B5" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="39" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="24" t="s">
@@ -14399,10 +14450,10 @@
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="39" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="24" t="s">
@@ -14548,10 +14599,10 @@
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="39" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="24" t="s">
@@ -14694,13 +14745,11 @@
       </c>
     </row>
     <row r="8" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="30"/>
+      <c r="A8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="31"/>
+      <c r="C8" s="40"/>
       <c r="D8" s="31"/>
       <c r="E8" s="31"/>
       <c r="F8" s="31"/>
@@ -14749,12 +14798,12 @@
       <c r="AW8" s="32"/>
     </row>
     <row r="9" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="22">
         <f>SUM(COUNTIF(B3:B8,"=DL*"))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="22">
         <f t="shared" ref="C9:AW9" si="0">SUM(COUNTIF(C3:C8,"=DL*"))</f>
@@ -15148,7 +15197,7 @@
       </c>
       <c r="B11" s="20" t="str">
         <f>IF(B10=0, CONCATENATE(B9), CONCATENATE(B9, ",",B10))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="20" t="str">
         <f t="shared" ref="C11:AW11" si="2">IF(C10=0, CONCATENATE(C9), CONCATENATE(C9, ",",C10))</f>
@@ -15396,8 +15445,8 @@
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
       <c r="F13" s="26"/>
@@ -15503,8 +15552,8 @@
       <c r="A14" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="28"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="39"/>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
       <c r="F14" s="24"/>
@@ -15590,8 +15639,8 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="28"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="39"/>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
@@ -15641,8 +15690,8 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="28"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="39"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
@@ -15692,8 +15741,8 @@
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="28"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="39"/>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
@@ -15743,8 +15792,8 @@
     </row>
     <row r="18" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="30"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="40"/>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
       <c r="F18" s="31"/>
@@ -15793,7 +15842,7 @@
       <c r="AW18" s="32"/>
     </row>
     <row r="19" spans="1:49" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="41" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="22">
@@ -16389,7 +16438,7 @@
       </c>
       <c r="B22" s="19" t="str">
         <f>IF(SUM(B10,B20) = 0, CONCATENATE(SUM(B9+B19)), CONCATENATE(SUM(B9,B19), ",", SUM(B10,B20)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="17" t="str">
         <f t="shared" ref="C22:AW22" si="6">IF(SUM(C10,C20) = 0, CONCATENATE(SUM(C9+C19)), CONCATENATE(SUM(C9,C19), ",", SUM(C10,C20)))</f>
@@ -16586,51 +16635,51 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A4">
-    <cfRule type="expression" dxfId="28" priority="14">
+    <cfRule type="expression" dxfId="27" priority="14">
       <formula>#REF!&gt;=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:AW1">
+    <cfRule type="expression" dxfId="26" priority="58">
+      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"DL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>"Dcar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
       <formula>"DL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
       <formula>"Dcar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
       <formula>"DL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="6" operator="equal">
       <formula>"Dcar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="7" operator="equal">
       <formula>"DL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
       <formula>"Dcar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="9" operator="equal">
       <formula>"DL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="10" operator="equal">
       <formula>"Dcar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
       <formula>"DL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
       <formula>"Dcar6"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AW1">
-    <cfRule type="expression" dxfId="15" priority="58">
-      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19644,51 +19693,51 @@
     <mergeCell ref="A12:AW12"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A4">
-    <cfRule type="expression" dxfId="14" priority="14">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>#REF!&gt;=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A1:AW1">
+    <cfRule type="expression" dxfId="12" priority="57">
+      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B3:AW10 B13:AW20">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"DL1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"Dcar1"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"DL2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"Dcar2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"DL3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"Dcar3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"DL4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
       <formula>"Dcar4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
       <formula>"DL5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="equal">
       <formula>"Dcar5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="11" operator="equal">
       <formula>"DL6"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
       <formula>"Dcar6"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AW1">
-    <cfRule type="expression" dxfId="1" priority="57">
-      <formula>AND(#REF!&gt;=$B$1, #REF! &lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
